--- a/docs/algorithm-interview-learning/cards/algorithm-interview-lesson-01-constraint-driven-selection-oral.xlsx
+++ b/docs/algorithm-interview-learning/cards/algorithm-interview-lesson-01-constraint-driven-selection-oral.xlsx
@@ -36,26 +36,26 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">面对陌生算法题，怎样在 45–90 秒内说明约束、基线、候选和结论边界？</t>
+          <t xml:space="preserve">如何从约束推导可辩护的算法方案？</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：先把约束转成方案的开关，再用可验证基线定位重复工作，最后只陈述证据支持的结论。
-• [T#B#澄清]：按数据特征、语义要求、访问模型、资源权限提问，并说明每项怎样改变候选。
-• [T#B#基线]：定义解空间，证明完整性，解释工作量语义并定位瓶颈。
-• [T#B#筛选]：逐项说明候选违反或利用了哪些已确认约束，并保留剩余未知。
-[T#B,!c47f17#边界]：没有下界证明时，只能说当前候选受阻或尚无有效方案，不能宣称全局无解或最优。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：在 45–90 秒内串起约束、基线、筛选与结论。
+• [T#B#澄清]：按数据、语义、访问与资源条件，解释哪些方案可用。
+• [T#B#基线]：说明解空间覆盖、工作量及重复工作。
+• [T#B#筛选]：将每个候选与已确认约束逐项对照。
+[T#B,!c47f17#边界]：未找到优化时，保留未知；没有下界论证就不宣称全局最优或不可能。</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">约束按稳定维度组织并映射到方案；基线说明完整性、工作量与瓶颈；候选方向与已确认约束绑定；结论明确剩余未知且不越界</t>
+          <t xml:space="preserve">约束能映射到方案变化；基线交代完整性、成本与重复工作；候选与约束逐项对应；结论保留未知且不过度推断</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lesson 01 学习记录｜要点、纠错、高价值问题</t>
+          <t xml:space="preserve">算法 01 日志 · 约束、基线与候选边界</t>
         </is>
       </c>
     </row>

--- a/docs/algorithm-interview-learning/cards/algorithm-interview-lesson-01-constraint-driven-selection-oral.xlsx
+++ b/docs/algorithm-interview-learning/cards/algorithm-interview-lesson-01-constraint-driven-selection-oral.xlsx
@@ -36,21 +36,21 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">如何从约束推导可辩护的算法方案？</t>
+          <t xml:space="preserve">向面试官说明 Two Sum 的解题过程：给定数组和 target，要求返回两个不同原下标，使元素和等于 target；访问方式、修改权限和空间限制尚待澄清。请用 45–90 秒说明如何从约束走到可验证基线、筛选优化，并在候选受阻时给出有依据的结论。</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：在 45–90 秒内串起约束、基线、筛选与结论。
-• [T#B#澄清]：按数据、语义、访问与资源条件，解释哪些方案可用。
-• [T#B#基线]：说明解空间覆盖、工作量及重复工作。
-• [T#B#筛选]：将每个候选与已确认约束逐项对照。
-[T#B,!c47f17#边界]：未找到优化时，保留未知；没有下界论证就不宣称全局最优或不可能。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：我会先确认哪些操作被允许，再给出能验证的基线，针对重复工作提出候选，并让最终结论严格对应已检查的证据。
+• [T#B#澄清]：先问输入规模、值域和顺序，确认是否返回原下标、能否随机访问或重读、能否修改输入，以及额外空间上限。这些答案分别决定成本是否可接受、基线能否执行，以及排序或保存历史是否可用。
+• [T#B#基线]：若输入允许重复访问，基线就是枚举所有不同下标的无序对。只让第二个下标位于第一个之后，每对恰好检查一次，因此不会漏掉答案；最坏比较次数随 n 的平方增长，其中 n 是数组长度。
+• [T#B#筛选]：瓶颈是固定一个元素后反复查找补数。接下来逐项核对候选：重排输入是否允许，保存历史是否超出空间限制，固定值域或已有顺序能否提供其他方向，而不是只报一个熟悉算法的名字。
+[T#B,!c47f17#边界]：如果目前候选都违反约束，我会说尚未找到有效优化，并指出还需核对的条件；排除几个候选不等于证明基线最优，没有相应下界论证就不宣称所有更快算法都不存在。</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">约束能映射到方案变化；基线交代完整性、成本与重复工作；候选与约束逐项对应；结论保留未知且不过度推断</t>
+          <t xml:space="preserve">说清数据、输出、访问和资源条件，并解释它们怎样影响方案；基线可执行，且说明不同下标对的完整覆盖与最坏成本；从重复补数查询出发，把每个优化候选逐项对照约束；候选受阻时保留未知，区分暂未找到优化与已证明下界</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
